--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>7465.12</v>
+        <v>7430.99</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8344.139999999999</v>
+        <v>8294.139999999999</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1011.33</v>
+        <v>1005.27</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1767.43</v>
+        <v>1756.83</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>787.01</v>
+        <v>782.3</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5786.11</v>
+        <v>5751.44</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1780.31</v>
+        <v>1769.64</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3173.4</v>
+        <v>3154.38</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>5084.26</v>
+        <v>5053.79</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>955.84</v>
+        <v>950.11</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>3106.68</v>
+        <v>3088.06</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>8163.82</v>
+        <v>8114.89</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>6794.56</v>
+        <v>6753.84</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1065.6</v>
+        <v>1059.21</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2709.46</v>
+        <v>2693.22</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>18373.46</v>
+        <v>18263.34</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2422.53</v>
+        <v>2408.01</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1176.09</v>
+        <v>1169.04</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>5109.69</v>
+        <v>5079.06</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>9231.51</v>
+        <v>9176.18</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>44103.36</v>
+        <v>43503.75</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1331.67</v>
+        <v>1313.56</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>7580.96</v>
+        <v>7477.89</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>1098.1</v>
+        <v>1083.17</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>9942.76</v>
+        <v>9807.58</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>6726.16</v>
+        <v>6634.71</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1238.21</v>
+        <v>1221.37</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1358.91</v>
+        <v>1340.44</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>10362.42</v>
+        <v>10221.54</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>16930.46</v>
+        <v>16700.28</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1195.53</v>
+        <v>1179.27</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2305.82</v>
+        <v>2274.47</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1778.06</v>
+        <v>1753.89</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3307.62</v>
+        <v>3262.65</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>4465.61</v>
+        <v>4404.9</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2951.15</v>
+        <v>2925.98</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2543.76</v>
+        <v>2522.06</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>991.15</v>
+        <v>982.7</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>1060.31</v>
+        <v>1051.27</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19680.49</v>
+        <v>19512.63</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>1573.5</v>
+        <v>1560.07</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>31104.78</v>
+        <v>30839.48</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>1702.19</v>
+        <v>1687.67</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>12231.74</v>
+        <v>12127.42</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>1534.67</v>
+        <v>1521.58</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>830.8200000000001</v>
+        <v>823.73</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>30859.81</v>
+        <v>30596.59</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2026.56</v>
+        <v>2009.27</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>1570.16</v>
+        <v>1556.77</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>7966.43</v>
+        <v>7898.48</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>12237.33</v>
+        <v>12132.96</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>5760.18</v>
+        <v>5711.05</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>8035.21</v>
+        <v>7966.67</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>2040.14</v>
+        <v>2022.74</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>5262.78</v>
+        <v>5217.89</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>2764.19</v>
+        <v>2779.08</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>4386.51</v>
+        <v>4410.13</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1059.52</v>
+        <v>1065.23</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>3244.65</v>
+        <v>3262.13</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>6162.33</v>
+        <v>6195.51</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3008.91</v>
+        <v>3025.12</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>788.63</v>
+        <v>792.88</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4076.87</v>
+        <v>4098.82</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>34020.14</v>
+        <v>34203.34</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>7368.06</v>
+        <v>7407.74</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1133.38</v>
+        <v>1139.48</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>13704.34</v>
+        <v>13778.13</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>1026.07</v>
+        <v>1031.6</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>45510.18</v>
+        <v>45755.25</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>2118.6</v>
+        <v>2130.01</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>21642.47</v>
+        <v>21759.01</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>5370.94</v>
+        <v>5431</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>1472.51</v>
+        <v>1488.98</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8409.610000000001</v>
+        <v>8503.67</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>4983.95</v>
+        <v>5039.69</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>3000.38</v>
+        <v>3033.94</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>17277.82</v>
+        <v>17471.05</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>7375.57</v>
+        <v>7458.06</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>1755.98</v>
+        <v>1775.62</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>6774.47</v>
+        <v>6850.23</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>2389.71</v>
+        <v>2416.44</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>5781.17</v>
+        <v>5845.82</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>9023.879999999999</v>
+        <v>9124.799999999999</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1147.73</v>
+        <v>1160.56</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>1021.85</v>
+        <v>1033.28</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>786.74</v>
+        <v>795.54</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1208.96</v>
+        <v>1222.48</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>17634.18</v>
+        <v>17831.4</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4689.11</v>
+        <v>4741.55</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>813.5599999999999</v>
+        <v>819.72</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3697.67</v>
+        <v>3725.68</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11175.96</v>
+        <v>11260.61</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>3252.6</v>
+        <v>3277.23</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>6843.95</v>
+        <v>6895.79</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>19657.97</v>
+        <v>19806.86</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>8879.58</v>
+        <v>8946.84</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>11994.21</v>
+        <v>12085.05</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>894.16</v>
+        <v>897.55</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>1599.45</v>
+        <v>1605.51</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>16332.52</v>
+        <v>16394.4</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>14261.8</v>
+        <v>14315.83</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>1748.89</v>
+        <v>1755.52</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>1000.9</v>
+        <v>1004.7</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1119.53</v>
+        <v>1123.77</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>3246.81</v>
+        <v>3259.11</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1020.27</v>
+        <v>1024.13</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>839.5</v>
+        <v>842.6799999999999</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>1576.42</v>
+        <v>1582.39</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>3437.31</v>
+        <v>3450.33</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>4041.4</v>
+        <v>4056.71</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>14236.41</v>
+        <v>14290.34</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>8121.39</v>
+        <v>8152.16</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>6615.25</v>
+        <v>6640.31</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>3549.32</v>
+        <v>3562.77</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>7850.04</v>
+        <v>7879.78</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>4175.6</v>
+        <v>4191.42</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>1667.14</v>
+        <v>1673.46</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>1061.45</v>
+        <v>1065.47</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6943.28</v>
+        <v>6969.59</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>3597.47</v>
+        <v>3611.1</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>18463.02</v>
+        <v>18532.97</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3434.43</v>
+        <v>3447.44</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2486.49</v>
+        <v>2495.91</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1720.1</v>
+        <v>1726.61</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1447.55</v>
+        <v>1443.89</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>7793.23</v>
+        <v>7773.56</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2856.27</v>
+        <v>2849.06</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>4356.47</v>
+        <v>4345.47</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>2175.26</v>
+        <v>2169.77</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>25729</v>
+        <v>25664.04</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>1940.83</v>
+        <v>1935.93</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>22916.01</v>
+        <v>22858.15</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>2584.3</v>
+        <v>2577.77</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>1243.51</v>
+        <v>1240.37</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>958.17</v>
+        <v>955.75</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1424.28</v>
+        <v>1420.68</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>1108.32</v>
+        <v>1105.53</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>29194.01</v>
+        <v>29120.3</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>2661.18</v>
+        <v>2654.46</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>1040.37</v>
+        <v>1050.26</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>1113.91</v>
+        <v>1124.49</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>934.66</v>
+        <v>943.54</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1237.25</v>
+        <v>1249.01</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>6907.52</v>
+        <v>6973.14</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>1151.96</v>
+        <v>1162.9</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>906.54</v>
+        <v>915.15</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>1847.21</v>
+        <v>1864.76</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>38285.41</v>
+        <v>38649.15</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>2927.73</v>
+        <v>2955.54</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>2096.01</v>
+        <v>2115.93</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>14304.55</v>
+        <v>14440.45</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>9855.459999999999</v>
+        <v>9949.1</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>6398.03</v>
+        <v>6458.81</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>804.4299999999999</v>
+        <v>812.0700000000001</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>5160.03</v>
+        <v>5209.05</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>848.91</v>
+        <v>856.97</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>1645.21</v>
+        <v>1660.84</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1532.28</v>
+        <v>1546.84</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>8711.309999999999</v>
+        <v>8794.07</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>1423.3</v>
+        <v>1436.82</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>3353.09</v>
+        <v>3384.95</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>4994.36</v>
+        <v>5041.81</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>15368.97</v>
+        <v>15514.98</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3102.59</v>
+        <v>3132.07</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>1428.18</v>
+        <v>1441.74</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>1609.61</v>
+        <v>1621.6</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>5848.47</v>
+        <v>5892.04</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>788.5599999999999</v>
+        <v>794.4400000000001</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>18010.92</v>
+        <v>18145.1</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>22270.39</v>
+        <v>22436.31</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>2973.35</v>
+        <v>2995.51</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>5418.09</v>
+        <v>5458.45</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>4901.21</v>
+        <v>4937.72</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>15753.49</v>
+        <v>15870.85</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>34655.57</v>
+        <v>34913.75</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>3909.64</v>
+        <v>3938.77</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>5245.01</v>
+        <v>5284.08</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>11201.92</v>
+        <v>11285.37</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>21935.72</v>
+        <v>22099.14</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>819.6799999999999</v>
+        <v>825.79</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>818.3</v>
+        <v>824.4</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3149.81</v>
+        <v>3173.27</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2527.07</v>
+        <v>2545.9</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>10738.45</v>
+        <v>10631.36</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>77301.66</v>
+        <v>76530.75</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>25907.7</v>
+        <v>25649.33</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>16625.13</v>
+        <v>16459.33</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1898.84</v>
+        <v>1879.9</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1340.49</v>
+        <v>1327.12</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>850.52</v>
+        <v>842.04</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>11235.78</v>
+        <v>11123.73</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>2611.37</v>
+        <v>2585.32</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4968.24</v>
+        <v>4918.69</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1764.44</v>
+        <v>1746.85</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>901.21</v>
+        <v>892.22</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4209.89</v>
+        <v>4167.91</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3831.5</v>
+        <v>3793.29</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>789.33</v>
+        <v>785.87</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>839.5</v>
+        <v>835.8200000000001</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>1533.31</v>
+        <v>1526.59</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>1337.63</v>
+        <v>1331.77</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>1476.97</v>
+        <v>1470.49</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>18490.26</v>
+        <v>18409.21</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>20324.72</v>
+        <v>20235.63</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>9467.58</v>
+        <v>9426.08</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>6973.02</v>
+        <v>6942.45</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>2563.52</v>
+        <v>2552.29</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1665.96</v>
+        <v>1658.66</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4517.6</v>
+        <v>4468.46</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>1867.01</v>
+        <v>1846.7</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>3889.61</v>
+        <v>3847.3</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>2179.9</v>
+        <v>2156.19</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>1341.21</v>
+        <v>1326.62</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>4993.37</v>
+        <v>4939.06</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>3095.51</v>
+        <v>3061.83</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>3468.86</v>
+        <v>3431.12</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2568.84</v>
+        <v>2540.9</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>1259.69</v>
+        <v>1245.99</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>2074.08</v>
+        <v>2051.52</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>1767.49</v>
+        <v>1748.26</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>953.59</v>
+        <v>943.22</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>3874.31</v>
+        <v>3832.16</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>12166.32</v>
+        <v>12033.97</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>981.77</v>
+        <v>971.09</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>1050.22</v>
+        <v>1038.8</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>16605.78</v>
+        <v>16425.14</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>2525.86</v>
+        <v>2498.38</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2201.99</v>
+        <v>2178.04</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>8264.16</v>
+        <v>8174.26</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>7862.33</v>
+        <v>7776.8</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>9747.82</v>
+        <v>9641.780000000001</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>7414.47</v>
+        <v>7333.82</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>1205.14</v>
+        <v>1192.03</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>7829.23</v>
+        <v>7744.06</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>1181.2</v>
+        <v>1168.35</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>12990.63</v>
+        <v>12961.15</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>11639.37</v>
+        <v>11612.95</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>2192.44</v>
+        <v>2187.46</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>9408.879999999999</v>
+        <v>9387.52</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>867.71</v>
+        <v>865.74</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>1861.2</v>
+        <v>1856.97</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>1327.09</v>
+        <v>1324.08</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>7349.38</v>
+        <v>7332.7</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>1530.16</v>
+        <v>1526.39</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>860.78</v>
+        <v>858.65</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>15693.7</v>
+        <v>15654.94</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>1452.14</v>
+        <v>1448.55</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>1225.76</v>
+        <v>1222.73</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>4591.17</v>
+        <v>4579.83</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>13453.06</v>
+        <v>13419.84</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>1829.48</v>
+        <v>1838.47</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>788.21</v>
+        <v>792.08</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>1498.31</v>
+        <v>1505.67</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>2562.45</v>
+        <v>2575.04</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>916.53</v>
+        <v>921.04</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>15782.03</v>
+        <v>15859.55</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>8743.08</v>
+        <v>8786.030000000001</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>32009.65</v>
+        <v>32166.89</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>8790.34</v>
+        <v>8833.52</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>34173.94</v>
+        <v>34341.81</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>3955.3</v>
+        <v>3974.73</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>919.36</v>
+        <v>923.87</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>870.2</v>
+        <v>874.47</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>1124.94</v>
+        <v>1130.47</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>888.63</v>
+        <v>892.99</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>4299.09</v>
+        <v>4320.21</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>38897.77</v>
+        <v>39026.8</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>3048.67</v>
+        <v>3058.78</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>33288.81</v>
+        <v>33399.24</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>4018.63</v>
+        <v>4031.96</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>2506.58</v>
+        <v>2514.89</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>2583.79</v>
+        <v>2592.36</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>2784.69</v>
+        <v>2793.93</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>1623.09</v>
+        <v>1628.47</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>5725.43</v>
+        <v>5744.42</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>9778.879999999999</v>
+        <v>9811.32</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>1900.17</v>
+        <v>1906.47</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>1346.14</v>
+        <v>1350.61</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>3779.32</v>
+        <v>3791.86</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1769.15</v>
+        <v>1775.02</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>1143.13</v>
+        <v>1146.92</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>1516.18</v>
+        <v>1521.21</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>11870.07</v>
+        <v>11909.44</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>20953.11</v>
+        <v>21022.62</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>27928.15</v>
+        <v>28020.8</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>3028.33</v>
+        <v>3038.37</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>2570.27</v>
+        <v>2578.8</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2256.68</v>
+        <v>2264.17</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2256.68</v>
+        <v>2264.17</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>4918.36</v>
+        <v>4934.67</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>881.72</v>
+        <v>884.53</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>824.8</v>
+        <v>827.4299999999999</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>1539.55</v>
+        <v>1544.45</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>4242.54</v>
+        <v>4256.04</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>6329.32</v>
+        <v>6349.47</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>2201.99</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3227.59</v>
+        <v>3237.87</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>1596.21</v>
+        <v>1601.29</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>17561.4</v>
+        <v>17617.3</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>3919.07</v>
+        <v>3931.54</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>1582.6</v>
+        <v>1587.63</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>14215.71</v>
+        <v>14260.96</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>5321.69</v>
+        <v>5338.63</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>1556.71</v>
+        <v>1561.67</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>8581.17</v>
+        <v>8608.48</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2489.67</v>
+        <v>2497.59</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>1130.16</v>
+        <v>1133.76</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>1256.59</v>
+        <v>1260.59</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>9312.84</v>
+        <v>9342.48</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>7544.3</v>
+        <v>7584.42</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>3212.65</v>
+        <v>3229.74</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>3208.86</v>
+        <v>3225.92</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>4409.28</v>
+        <v>4432.73</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>3148.79</v>
+        <v>3165.53</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>34510.08</v>
+        <v>34693.59</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>1658.8</v>
+        <v>1667.62</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>4733.52</v>
+        <v>4758.69</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>7478.81</v>
+        <v>7518.57</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>8832.950000000001</v>
+        <v>8879.92</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>2165.83</v>
+        <v>2177.35</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>38809.58</v>
+        <v>39015.95</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>26762.15</v>
+        <v>26904.46</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>1030.73</v>
+        <v>1036.21</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4119.98</v>
+        <v>4141.89</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>1094.88</v>
+        <v>1100.7</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>792.52</v>
+        <v>796.73</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>788.21</v>
+        <v>792.4</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC may-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -8174,7 +8174,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9333,7 +9333,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9455,7 +9455,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9638,7 +9638,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10187,7 +10187,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12261,7 +12261,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13237,7 +13237,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13786,7 +13786,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13908,7 +13908,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -14579,7 +14579,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -15738,7 +15738,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15982,7 +15982,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16592,7 +16592,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16653,7 +16653,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17202,7 +17202,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -18178,7 +18178,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -19825,7 +19825,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
@@ -971,7 +971,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Unidad Contable Disalcar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS ALAMOS</t>
+          <t>I MUNICIPALIDAD DE LOS ALAMOS DEPTO COMUNAL</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Semi Abierto Victori</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hospital de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>ALA BASE N°1</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Gendarmeria de Chile Centro de Educación y Trabajo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>BASE INFANTERIA DE MARINA CONCON</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA ORLANDO ANTONIO</t>
+          <t>Comercializadora orlando antonio</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>IMPORTADORA Y COMERCIAL MIR Y CRUZ SPA</t>
+          <t>IMPORTADORA Y COMERCIAL MIR Y CRUZ SpA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Comandancia General del Cuerpo I.M.</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>ESCUELA NAVAL "ARTURO PRAT"</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>CENTRO DE ABASTECIMIENTO (T)</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cañete - Educación</t>
+          <t>I MUNICIPALIDAD DE CANETE</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - IX Zona Araucania</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>JEFATURA ADMINISTRATIVA Y LOGISTICA DE LA GUARNICION COYHAIQUE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>I MUNICIPALIDAD DE COIHUECO</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8113,7 +8113,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>COMERCIAL IBL SPA</t>
+          <t>Comercial IBL SpA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -8845,7 +8845,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Gendarmería de Chile - Dirección Regional de Coquimbo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9328,7 +9328,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cabrero</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9572,7 +9572,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9877,12 +9877,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10060,7 +10060,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>VIII Zona de Carabineros Bio Bío</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10121,7 +10121,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad De Curanilahue - Educación</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10375,7 +10375,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo Colina 1</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -11107,7 +11107,7 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
@@ -11168,7 +11168,7 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>Quality Rubber S.A.</t>
+          <t>QUALITY RUBBER S.A.</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
@@ -11219,12 +11219,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11341,7 +11341,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Dirección General de Carabineros de Chile</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -11402,7 +11402,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>I MUNICIPALIDAD DE LOS ANGELES</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS IX ZONA</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12927,12 +12927,12 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE RECOLETA</t>
+          <t>I MUNICIPALIDAD DE RECOLETA</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13110,12 +13110,12 @@
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>IIª Brigada Aérea</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13720,7 +13720,7 @@
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo CDP Villarrica</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -14147,7 +14147,7 @@
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>FONDO PARA HOSPITALES DE CARABINEROS DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -14391,7 +14391,7 @@
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="I234" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J234" t="inlineStr">
@@ -14767,7 +14767,7 @@
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>REGIMIENTO 12 "SANGRA"</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14879,7 +14879,7 @@
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Corporación Municipal Desarrollo Social Antofagast</t>
+          <t>CORP MUNICIPAL DE DESARROLLO SOCIAL DE A</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Servicio Electoral</t>
+          <t>SERVICIO ELECTORAL</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -15845,7 +15845,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -16109,7 +16109,7 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;AMP; EXPORTADORA UNINNOV EIRL</t>
+          <t>LUIS LEONARDO CALDERON NETTLE IMPORTADORA &amp;amp; EXPORTADORA UNINNOV EIRL</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -16648,7 +16648,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Jefatura Adm. y Log. del Campo Militar Austral</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -16709,7 +16709,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -16953,7 +16953,7 @@
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Valparaiso</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17502,7 +17502,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>DIRECCION DE SEGURIDAD Y OPERACIONES MARITIMAS</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -17624,7 +17624,7 @@
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Coquimbo</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -18112,7 +18112,7 @@
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -18295,7 +18295,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo del Centro de Cumpli</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -18539,7 +18539,7 @@
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Servicio local de educación pública de Valdivia</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE VALDIVIA</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -18722,7 +18722,7 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -18783,7 +18783,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE DESARROLLO SOCIAL COLINA</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -18966,7 +18966,7 @@
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Academia Politécnica Naval</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -19627,7 +19627,7 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Nacimiento - Departamento de educación</t>
+          <t>I MUNICIPALIDAD DE NACIMIENTO</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -20196,7 +20196,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>Comercial Agustin Limitada</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
@@ -684,7 +684,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +749,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +814,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +879,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +944,11 @@
           <t>76.698.741-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1375,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1501,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1566,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1692,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1757,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1822,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2070,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2135,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2200,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2509,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2574,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2639,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2704,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2891,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3200,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3387,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3513,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3639,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3765,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3830,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4017,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4082,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4330,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4517,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4582,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4647,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4712,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +4960,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5086,11 @@
           <t>77.601.843-0</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5517,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5643,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5708,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5895,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6082,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6208,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6273,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6399,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6769,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7322,11 @@
           <t>77.685.821-8</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7448,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7513,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7639,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7704,11 @@
           <t>52.003.040-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +7830,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +7956,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8021,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8208,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8334,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8399,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8464,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8529,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +8838,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9147,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9212,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9277,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9464,11 @@
           <t>77.352.453-K</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9529,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +9777,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +9842,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10029,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10277,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10464,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +10712,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +10960,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11086,11 @@
           <t>77.601.267-K</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11151,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11338,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +11586,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +11651,11 @@
           <t>77.787.617-1</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +11716,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +11964,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12029,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12216,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12281,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12346,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12472,11 @@
           <t>76.378.846-6</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +12659,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +12846,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13033,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13159,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13346,11 @@
           <t>76.712.337-K</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13411,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13476,11 @@
           <t>76.148.628-4</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14212,11 @@
           <t>77.714.558-4</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14277,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +14586,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +14712,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +14899,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +14964,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15029,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15216,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15281,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15407,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +15594,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +15781,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +16761,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +16948,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17196,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17261,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +17448,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +17574,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +17761,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +17948,11 @@
           <t>76.317.833-1</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18074,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18261,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +18509,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +18574,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +18639,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +18704,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +18830,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19139,11 @@
           <t>76.532.399-1</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +19448,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +19574,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +19761,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +19826,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +19952,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +20322,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +20387,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +20452,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +20761,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +20826,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
+++ b/docs/oc-mensuales/productos-y-servicios-de-ferreteria/may-2026.xlsx
@@ -10651,7 +10651,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15155,7 +15159,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20700,7 +20708,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
